--- a/data/Mothers datasheet.xlsx
+++ b/data/Mothers datasheet.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/cariya_wallet/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/CARIYA/cariya_wallet/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB72EC29-92F6-5E43-9679-E9E8C145BE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4536024-9027-E642-85CA-31DF265D5448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29220" yWindow="1440" windowWidth="28800" windowHeight="16100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clean data sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Profiles" sheetId="2" r:id="rId2"/>
+    <sheet name="Activity" sheetId="3" r:id="rId3"/>
+    <sheet name="AddActivity" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>Partner</t>
   </si>
@@ -100,13 +103,43 @@
   </si>
   <si>
     <t>4/1</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Mbarara</t>
+  </si>
+  <si>
+    <t>Masaka</t>
+  </si>
+  <si>
+    <t>Mpigi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile number </t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>National ID</t>
+  </si>
+  <si>
+    <t>Education Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,8 +173,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,8 +194,20 @@
         <bgColor rgb="FF4A86E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF4A86E8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -178,11 +230,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -203,6 +266,32 @@
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,4 +664,239 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB176ED-447E-BB45-A8E2-0005444E8622}">
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.5" customWidth="1"/>
+    <col min="5" max="5" width="30.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" s="18" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="5">
+        <v>782781759</v>
+      </c>
+      <c r="D2" s="5">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5">
+        <v>753472153</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="10">
+        <v>726711993</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="C6" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3FC5AD-B10C-D64B-AABF-E2ED81816600}">
+  <dimension ref="A1:V6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="17"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{815931E9-5F43-3540-9E3E-44FFCFF0D9CC}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="23" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>